--- a/ttl_long/AdHoc_Net_18.xlsx
+++ b/ttl_long/AdHoc_Net_18.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>206</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>175</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>350</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>315</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>255</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>446</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>458</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>464</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>605</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>507</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>693</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>587</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>669</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>804</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>796</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>801</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>934</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>991</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>984</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>986</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1150</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1029</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1270</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1277</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1173</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1428</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1433</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>313</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1360</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1393</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1464</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>344</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1454</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1583</t>
         </is>
       </c>
     </row>
@@ -1072,46 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1549</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1588</t>
+          <t>1534</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1181,7 +1147,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1203,7 +1169,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1225,7 +1191,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1247,7 +1213,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1269,7 +1235,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1291,7 +1257,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1313,7 +1279,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1335,7 +1301,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1357,7 +1323,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1379,7 +1345,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1440,12 +1406,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1467,7 +1433,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1489,7 +1455,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1511,7 +1477,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1533,7 +1499,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1555,7 +1521,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1577,7 +1543,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1594,12 +1560,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1616,12 +1582,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1643,7 +1609,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1660,12 +1626,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1682,12 +1648,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1704,12 +1670,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1726,12 +1692,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1753,7 +1719,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1770,12 +1736,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1792,12 +1758,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1814,12 +1780,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1841,7 +1807,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1858,12 +1824,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1880,12 +1846,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1902,12 +1868,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1929,7 +1895,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1946,12 +1912,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1968,12 +1934,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1995,7 +1961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2012,12 +1978,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2034,7 +2000,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2083,7 +2049,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2100,12 +2066,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2127,7 +2093,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2144,12 +2110,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2193,7 +2159,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2215,7 +2181,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2232,12 +2198,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2254,12 +2220,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2276,12 +2242,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2298,12 +2264,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2320,7 +2286,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2342,12 +2308,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2364,12 +2330,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2386,12 +2352,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2408,12 +2374,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2430,12 +2396,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2452,12 +2418,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2474,12 +2440,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2496,12 +2462,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2518,12 +2484,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2540,7 +2506,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2562,12 +2528,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2584,12 +2550,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2606,12 +2572,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2628,12 +2594,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2650,12 +2616,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2672,12 +2638,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2694,12 +2660,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2716,12 +2682,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2738,12 +2704,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2760,7 +2726,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2782,12 +2748,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2804,12 +2770,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2826,12 +2792,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2848,12 +2814,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,12 +2836,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2892,12 +2858,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2914,12 +2880,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2936,12 +2902,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2958,12 +2924,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2980,12 +2946,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3002,12 +2968,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3024,12 +2990,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3046,12 +3012,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3068,12 +3034,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3090,12 +3056,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3112,12 +3078,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3134,12 +3100,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3156,12 +3122,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3178,12 +3144,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3200,12 +3166,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3222,12 +3188,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3244,12 +3210,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3266,12 +3232,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3288,12 +3254,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3310,12 +3276,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3332,12 +3298,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3354,12 +3320,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3376,12 +3342,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3398,12 +3364,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3420,12 +3386,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3442,12 +3408,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3464,12 +3430,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3486,12 +3452,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3500,248 +3466,6 @@
         </is>
       </c>
       <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3780,7 +3504,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3790,7 +3514,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -3816,7 +3540,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_18.xlsx
+++ b/ttl_long/AdHoc_Net_18.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>168</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>263</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>430</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>342</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>466</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>502</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>653</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>660</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>659</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>778</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>741</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>725</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>910</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>847</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>909</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>953</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>266</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1032</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1158</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1203</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1085</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1239</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>133</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1293</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1226</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1288</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>241</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1399</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1409</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1526</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,63 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1559</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1556</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1567</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1147,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1169,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1191,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1213,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1235,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1257,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1274,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1367,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1389,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1406,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1433,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1455,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1472,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1494,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1516,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1538,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1560,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1582,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1604,7 +1655,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1626,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1648,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1670,7 +1721,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1692,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1736,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1758,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1780,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1807,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1824,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1851,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1873,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1912,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1961,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1978,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2000,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2049,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2071,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2093,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2115,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2137,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2159,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2181,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2220,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2242,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2264,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2286,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2308,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2335,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2352,7 +2403,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2374,7 +2425,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2396,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2418,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2440,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2462,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2484,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2506,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2528,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2550,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2572,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2594,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2616,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2638,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2660,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2682,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2704,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2726,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2748,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2770,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2792,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2814,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2836,7 +2887,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2858,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2880,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2902,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2924,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2946,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2968,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2990,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3012,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3034,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3056,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3078,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3100,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3122,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3144,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3166,7 +3217,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3188,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3210,7 +3261,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3232,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3254,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3276,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3298,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3320,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3342,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3364,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3386,7 +3437,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3408,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3430,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3452,20 +3503,328 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3504,7 +3863,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3514,7 +3873,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -3534,7 +3893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_18.xlsx
+++ b/ttl_long/AdHoc_Net_18.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>158</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>255</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>288</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>248</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>343</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>347</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>351</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>529</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>570</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>482</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>590</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>628</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>603</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>703</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>823</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>773</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>893</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>927</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>833</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>978</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>141</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>916</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1119</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1136</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>287</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1096</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1192</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1305</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1229</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1433</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1447</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1397</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1427</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1430</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1528</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1586</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1675</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,7 +2953,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3657,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3693,138 +3693,6 @@
         </is>
       </c>
       <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3863,7 +3731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3873,7 +3741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
